--- a/results/Int Task Remove ACC -0.7/Rando_fi_explain.xlsx
+++ b/results/Int Task Remove ACC -0.7/Rando_fi_explain.xlsx
@@ -1148,268 +1148,268 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.02403237433979e-05</v>
+        <v>0.0003840434842290897</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.001866296389203498</v>
+        <v>-0.0009888907786906177</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0008355362294161495</v>
+        <v>0.001592666721944175</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001486680983402746</v>
+        <v>0.001513686434538332</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0003544523007488887</v>
+        <v>-0.001549740234492775</v>
       </c>
       <c r="H3" t="n">
-        <v>0.003471857898887658</v>
+        <v>0.001759918038799929</v>
       </c>
       <c r="I3" t="n">
-        <v>1.619076324722912e-05</v>
+        <v>-3.932815874082562e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.002336647613102202</v>
+        <v>-0.0008763670051848228</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01632055228434073</v>
+        <v>0.01706347936202696</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02012741657781438</v>
+        <v>0.01818857876307781</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.001741816374436943</v>
+        <v>-0.002954921844608374</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0002399768474722052</v>
+        <v>-0.001100807432478611</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004233767570583784</v>
+        <v>0.002822043061661744</v>
       </c>
       <c r="P3" t="n">
-        <v>0.003625813921684121</v>
+        <v>0.004352735252028049</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01113521192334376</v>
+        <v>0.01131315727151626</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.0007305428222093701</v>
+        <v>0.0003852956455882763</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0008087957520117817</v>
+        <v>-9.479580613984675e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0002935385241996081</v>
+        <v>-0.001597048510898037</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0001753105972358504</v>
+        <v>9.917107911562532e-05</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0001638395754103827</v>
+        <v>0.0001955794515634324</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0008714994247245192</v>
+        <v>0.0001017824674593958</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.002059652745762434</v>
+        <v>0.0001870618085535136</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001884012130765468</v>
+        <v>0.001779105266133359</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.002550730371179727</v>
+        <v>0.001857942320779672</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.002076207602268531</v>
+        <v>0.001328472527455598</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0001183697912500026</v>
+        <v>-0.0001401307628396686</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.002403691212311519</v>
+        <v>0.005066408184568075</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.004236112592128479</v>
+        <v>-0.0008586027176714902</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.0001090374737210398</v>
+        <v>-0.000678933737562455</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.00105054173751396</v>
+        <v>-0.00421106232003809</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0002802851898316483</v>
+        <v>-3.786755561563606e-05</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0003046723376141292</v>
+        <v>0.0002107297707834932</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.001450308661779204</v>
+        <v>-0.0009923219947381222</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.00240990826931922</v>
+        <v>-0.004658662200700788</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0001480454520176644</v>
+        <v>-0.0001340705140148979</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.0002683609280105371</v>
+        <v>-0.0003442970323483219</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.001766315676901126</v>
+        <v>0.002173716718887052</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.001219024083235628</v>
+        <v>1.338428357156795e-05</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.0002123836333315332</v>
+        <v>0.0005916723667022952</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.001442126790471574</v>
+        <v>0.001705887425404313</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.00310790535862246</v>
+        <v>-0.002500300737566167</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.0005017755064392237</v>
+        <v>0.001405969210229111</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.002464169547151901</v>
+        <v>0.002863106455963873</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.001571312643679923</v>
+        <v>0.0008936255519712399</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.0004406830578045738</v>
+        <v>-0.0005313812995074596</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.0005093144817360096</v>
+        <v>0.0001183818554812611</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.0002942767394733148</v>
+        <v>8.08402561071886e-05</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.0006306747157503055</v>
+        <v>0.002019264117303267</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.001119981256970466</v>
+        <v>0.001296460553803076</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.005177979425197321</v>
+        <v>-0.002390837930459958</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.002517083780651764</v>
+        <v>-0.004063649227237057</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.361087104082356e-06</v>
+        <v>0.0003293594257402244</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.235943610288674e-05</v>
+        <v>0.0004940616184324498</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.0003530432584568833</v>
+        <v>-0.0004941112945989379</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.003811486272552116</v>
+        <v>-0.004557917131010903</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.002253379372220987</v>
+        <v>0.002256849464716446</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1.110223024625157e-18</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.0002621497264420258</v>
+        <v>-3.855447515453414e-05</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.001481223516523794</v>
+        <v>-0.0005020077157965441</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.002138957114093868</v>
+        <v>-0.001345035104371833</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.0004700747896714386</v>
+        <v>-2.0628123381583e-05</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.0002510502154350914</v>
+        <v>0.002067500094838285</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.004943941833459186</v>
+        <v>-0.003862195977113903</v>
       </c>
       <c r="BO3" t="n">
-        <v>-2.482033957017845e-05</v>
+        <v>0.001039190988404741</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.001752999266149011</v>
+        <v>-0.0005143636659339578</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.772556172717875e-05</v>
+        <v>0.0004164911183332842</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.001150430209044533</v>
+        <v>0.001143697197333469</v>
       </c>
       <c r="BS3" t="n">
-        <v>-1.906513396916851e-05</v>
+        <v>0.001245858787799754</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0.0003447281777232524</v>
+        <v>0.0002859404834441548</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.004178788328332328</v>
+        <v>0.005938165129207038</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.0003785975900304541</v>
+        <v>-0.0001572576330549181</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.002004666418590404</v>
+        <v>0.002262919669766688</v>
       </c>
       <c r="BX3" t="n">
-        <v>-3.725003729473708e-05</v>
+        <v>0.0002514237853912183</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.0003104692085614513</v>
+        <v>0.000292121860401564</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.001029604573987935</v>
+        <v>-0.0007826303813597702</v>
       </c>
       <c r="CA3" t="n">
-        <v>-2.249289085458961e-05</v>
+        <v>8.882153038929364e-06</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0.0001900564599815802</v>
+        <v>0.0005499697063318054</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.002804765458522924</v>
+        <v>-0.0005926271869706623</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.0002047854504882318</v>
+        <v>-3.24336184367735e-05</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.000257192016190888</v>
+        <v>0.0002474585915883498</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.0003310593403777184</v>
+        <v>0.001133468116801042</v>
       </c>
       <c r="CG3" t="n">
-        <v>-5.669598534536868e-05</v>
+        <v>0.0001058594464011474</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.001328566659052052</v>
+        <v>-0.0001472400547664798</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.0002610400025283233</v>
+        <v>9.293246763213306e-05</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.0005840032938801898</v>
+        <v>0.002628994643352507</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.4663415806252e-05</v>
+        <v>0.0002259884850394545</v>
       </c>
     </row>
     <row r="4">
@@ -1419,268 +1419,268 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003347715358459845</v>
+        <v>0.00608265476544765</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006844792764381081</v>
+        <v>0.006188472781821348</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006471933617760031</v>
+        <v>0.004949979745674195</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002870931559164226</v>
+        <v>0.002270122011309014</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002671211205343379</v>
+        <v>0.00702336635344646</v>
       </c>
       <c r="H4" t="n">
-        <v>0.004461681066223895</v>
+        <v>0.002973035453494513</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0002084769053301601</v>
+        <v>0.0002842425260727113</v>
       </c>
       <c r="J4" t="n">
-        <v>0.006110596326108947</v>
+        <v>0.004154398489984011</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01243910287363815</v>
+        <v>0.01241711264961045</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01419371376583478</v>
+        <v>0.01367083458913055</v>
       </c>
       <c r="M4" t="n">
-        <v>0.005686093775307721</v>
+        <v>0.003774468070594077</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007568592838441144</v>
+        <v>0.007036520716592741</v>
       </c>
       <c r="O4" t="n">
-        <v>0.008588566241422893</v>
+        <v>0.007761968095994796</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01410134930804231</v>
+        <v>0.01474954663627364</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0103385073789091</v>
+        <v>0.01089773669718217</v>
       </c>
       <c r="R4" t="n">
-        <v>0.003565246562091525</v>
+        <v>0.003607670302450577</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002963676920710596</v>
+        <v>0.003552131546579987</v>
       </c>
       <c r="T4" t="n">
-        <v>0.003016962291538651</v>
+        <v>0.004634146859131628</v>
       </c>
       <c r="U4" t="n">
-        <v>0.004288928811775208</v>
+        <v>0.002094735295967372</v>
       </c>
       <c r="V4" t="n">
-        <v>0.000482592425647554</v>
+        <v>0.0004085844782134653</v>
       </c>
       <c r="W4" t="n">
-        <v>0.01067692643295276</v>
+        <v>0.009550692499708894</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004752379296230386</v>
+        <v>0.003693442515991051</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.003400461339361584</v>
+        <v>0.002003075092749179</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.00242291637597804</v>
+        <v>0.001431786421917306</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.003198327282270097</v>
+        <v>0.002305021965244637</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0005568184791445633</v>
+        <v>0.0008285621133317979</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.005998317691719952</v>
+        <v>0.003551332381396688</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.01099729300553189</v>
+        <v>0.009709060444317505</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.004022540711811371</v>
+        <v>0.005244516976851189</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.007669524362517953</v>
+        <v>0.006929647500506257</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0006107829980933079</v>
+        <v>0.0006055240767710715</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0004189384581644041</v>
+        <v>0.001182556776339831</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.005681064683535651</v>
+        <v>0.003219617070768633</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.005358209115223866</v>
+        <v>0.0104250455795006</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0007562727684302116</v>
+        <v>0.0009193344188086832</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0006782403389030558</v>
+        <v>0.0008265861778038691</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.002565707933566632</v>
+        <v>0.003446845636500915</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.003733472175209261</v>
+        <v>0.005250483547606372</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.0006727768912370299</v>
+        <v>0.002100065807751561</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.002970755508497985</v>
+        <v>0.002495376102546641</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.003536283100243959</v>
+        <v>0.00522984444309474</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.002579580372038968</v>
+        <v>0.00472297635933385</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.005925507016634373</v>
+        <v>0.007156038594934793</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.002800128395655829</v>
+        <v>0.003594235341360999</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.003156750074466598</v>
+        <v>0.003784896105281667</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.004956299680457291</v>
+        <v>0.003987099297223433</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0005754799044826726</v>
+        <v>0.0007708354993183565</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.003505346183637095</v>
+        <v>0.002766181845796967</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.006532731392201659</v>
+        <v>0.007504471310004081</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.01190322985929429</v>
+        <v>0.008319916632281783</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.008312936119514504</v>
+        <v>0.008742788591014359</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.001007824516982732</v>
+        <v>0.001126404176555264</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.000670812606877086</v>
+        <v>0.001282233165526519</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.0005666576952051996</v>
+        <v>0.0005787636421228944</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.01056952175481001</v>
+        <v>0.009827337591100865</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.008147498255045637</v>
+        <v>0.009341734502297328</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>3.510833468576701e-18</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.000927382698230631</v>
+        <v>0.0004857196786999414</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.003457724730250356</v>
+        <v>0.004341364334103085</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.006039362076001331</v>
+        <v>0.007415241999632699</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0007269788933251856</v>
+        <v>0.001335364317712705</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.006221611740349442</v>
+        <v>0.004155702358436527</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.007042067731692942</v>
+        <v>0.01104139369213902</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.003039220647757961</v>
+        <v>0.0035613537813756</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.005817323424508182</v>
+        <v>0.002152722959802233</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0005725667126063987</v>
+        <v>0.001448114125488945</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.005626359998719626</v>
+        <v>0.004792425537179225</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.00336769595310046</v>
+        <v>0.003415869840660062</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.001575810075692248</v>
+        <v>0.001537933170707245</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.005079060232274519</v>
+        <v>0.01039504346698877</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.004124454278581853</v>
+        <v>0.00413300970734939</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.005895224769980146</v>
+        <v>0.004566158086909787</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0002530168584378742</v>
+        <v>0.0003842998306558776</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.002103334795429513</v>
+        <v>0.002372431315170219</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.001035273818222281</v>
+        <v>0.001650641095213857</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.000157986500709173</v>
+        <v>1.973346956786395e-05</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.001707661663011197</v>
+        <v>0.002514652684087806</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.002917302064060752</v>
+        <v>0.002704479140118331</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.0006825981293724651</v>
+        <v>8.388495026089337e-05</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.0008807936929446292</v>
+        <v>0.001336428152895795</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.003699248330091274</v>
+        <v>0.003058375078743104</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.00517452587402764</v>
+        <v>0.005525727299807814</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.002049933817370466</v>
+        <v>0.002061553717251624</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.001626566222998924</v>
+        <v>0.002736857396468256</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.004709416419873831</v>
+        <v>0.007665244598679477</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.002791341774418171</v>
+        <v>0.001817861289073644</v>
       </c>
     </row>
     <row r="5">
@@ -1690,268 +1690,268 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.005308168681804814</v>
+        <v>-0.007400828892835998</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.01595146493045276</v>
+        <v>-0.00764430577223092</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01564390665514259</v>
+        <v>-0.004062229904926584</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.004570923031554153</v>
+        <v>-0.002808112324493006</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.004045211183819131</v>
+        <v>-0.01616248919619712</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.00260106549670952</v>
+        <v>-0.003315571343990531</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0003361858190709111</v>
+        <v>-0.0003745318352060378</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.01145309263095589</v>
+        <v>-0.008940201302545903</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0007490636704119647</v>
+        <v>-0.002016709881878476</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002189570728896584</v>
+        <v>-0.005646787669259634</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.01195620858542203</v>
+        <v>-0.007048068416396313</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01412562665880278</v>
+        <v>-0.01780466724286953</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.00605012964563526</v>
+        <v>-0.003374777975133225</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.02035450516986702</v>
+        <v>-0.01414577931431868</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.003715718077263397</v>
+        <v>-0.01020347979946917</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.005022156573116665</v>
+        <v>-0.004544030084612949</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.006655142610198772</v>
+        <v>-0.006631142687981073</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.00671995263469507</v>
+        <v>-0.01193013617525164</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.00607490415806553</v>
+        <v>-0.002647233789411052</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0009048361934477778</v>
+        <v>-0.0004164187983343171</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.01066902446212794</v>
+        <v>-0.01794871794871795</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.01135358301386028</v>
+        <v>-0.008792184724689178</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.005013270421704563</v>
+        <v>-0.001873884592504449</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.0002808112324493073</v>
+        <v>-0.0006112469437653312</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.002545131695767966</v>
+        <v>-0.001436430317848458</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.0007176287051482322</v>
+        <v>-0.001368233194527047</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.007694584196507803</v>
+        <v>-0.0001775673276117162</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.03013617525162817</v>
+        <v>-0.02326820603907639</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.005986434680035435</v>
+        <v>-0.00988750740082891</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.01828369212621652</v>
+        <v>-0.01740132526649386</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.0005603066941905488</v>
+        <v>-0.0006203840472673528</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.0003667481662591676</v>
+        <v>-0.00123857269242108</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.01182542023002069</v>
+        <v>-0.007182151589242102</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.01110124333925397</v>
+        <v>-0.03206039076376556</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.0007696862048548914</v>
+        <v>-0.002141582391433672</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.001130279595478845</v>
+        <v>-0.002161042036708127</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.003048239124001173</v>
+        <v>-0.002189997040544533</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.00905337658507821</v>
+        <v>-0.007220748600058957</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.0005327019828351487</v>
+        <v>-0.001987899740708799</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.002959455460195293</v>
+        <v>-0.001803178484107637</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.01067531701562966</v>
+        <v>-0.01515689757252814</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.002870671796389434</v>
+        <v>-0.009420916162489246</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.01197286936007084</v>
+        <v>-0.01011235955056184</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.004544030084612993</v>
+        <v>-0.006295843520782452</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.003166617342408961</v>
+        <v>-0.004350399526487125</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.007962253022707222</v>
+        <v>-0.003802938634399378</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.0005305039787798727</v>
+        <v>-0.0008625817965496662</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.005214635551714197</v>
+        <v>-0.0009168704156479856</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.01377124747911265</v>
+        <v>-0.01339671564390671</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.02595104688882342</v>
+        <v>-0.02301930279458375</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.01810675317015634</v>
+        <v>-0.02278882166522621</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.001592450604541484</v>
+        <v>-0.001011302795954794</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.001061633736361001</v>
+        <v>-0.001189767995240931</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.00152693748199364</v>
+        <v>-0.001568975725281219</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.02391624889413156</v>
+        <v>-0.0277153558052435</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.01696917314894841</v>
+        <v>-0.01961970613656012</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.001002063071028603</v>
+        <v>-0.0008257151282807018</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.004494382022471877</v>
+        <v>-0.009997118985883091</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.01291654379239169</v>
+        <v>-0.01743010113027959</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.0005622965374371014</v>
+        <v>-0.001650456822870649</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.01618991447950463</v>
+        <v>-0.007634687409968377</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.02002304811293572</v>
+        <v>-0.03275713050993954</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.007549395458566854</v>
+        <v>-0.00378922439313204</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.006483937518420313</v>
+        <v>-0.003448275862068995</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.00123857269242118</v>
+        <v>-0.0005651397977394334</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.007279693486590089</v>
+        <v>-0.003996447602131447</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.007166027720436519</v>
+        <v>-0.003108348134991124</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.004099085815393732</v>
+        <v>-0.001568975725281252</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.002776957163958627</v>
+        <v>-0.009364844903988135</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.005865834633385391</v>
+        <v>-0.008664898320070747</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.003415857098088393</v>
+        <v>-0.003161004431314607</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.0003120124804992574</v>
+        <v>-0.0001181683899556862</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.004806841639634352</v>
+        <v>-0.00230905861456483</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.002831023296962598</v>
+        <v>-0.004973357015985791</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.0004321521175453258</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.003772472737990018</v>
+        <v>-0.001886236368994998</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.002974419988102273</v>
+        <v>-0.004759071980963703</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.002122015915119391</v>
+        <v>-0.0002652519893898919</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.001786273895330614</v>
+        <v>-0.0005014102162331224</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.006837606837606858</v>
+        <v>-0.001828369212621639</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.01049837805956948</v>
+        <v>-0.01125847332743887</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.005278678855794805</v>
+        <v>-0.004185086943707661</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.00228768411156377</v>
+        <v>-0.004766133806986395</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.007897210905672225</v>
+        <v>-0.01193633952254644</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.004322084073416199</v>
+        <v>-0.001805802249851995</v>
       </c>
     </row>
     <row r="6">
@@ -1961,268 +1961,268 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.002794838881695994</v>
+        <v>-0.003214605500524143</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.004071199253489186</v>
+        <v>-0.004677023797070717</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0006504311939362962</v>
+        <v>-0.001121265953358591</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0005878722312706586</v>
+        <v>0.0004176839094424123</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.002537229339553074</v>
+        <v>-0.004574293485344799</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001381775000076524</v>
+        <v>-4.255129033819971e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>-8.616769417952309e-05</v>
+        <v>-0.0002007341741232654</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.007175491036094786</v>
+        <v>-0.002601995920024316</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0101030022528551</v>
+        <v>0.008236288725484821</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01534558975589985</v>
+        <v>0.01488467032823907</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.003559002862382599</v>
+        <v>-0.00507601318112767</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.002199453972058879</v>
+        <v>-0.001905487859931459</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0004112772591116337</v>
+        <v>-0.001875093773839753</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.006452838606360129</v>
+        <v>-0.008348796570922554</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.005850719268741292</v>
+        <v>0.006414874507303739</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.003779448619461309</v>
+        <v>-0.002608244524958264</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.001583376568717243</v>
+        <v>-0.002782978243579493</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.001042769434376867</v>
+        <v>-0.003179325507345096</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.001842747257772753</v>
+        <v>-0.001084441195400707</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0001432942370823392</v>
+        <v>-0.0001170351477878168</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.006013300424430415</v>
+        <v>-0.005807094825935127</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.002125510131188124</v>
+        <v>-0.0006734224425157171</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.0003916571735632923</v>
+        <v>0.0005812096590214949</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0008552243104737429</v>
+        <v>0.0009401341959883513</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.000577354205934702</v>
+        <v>-0.0003539039862370114</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0001482206122942781</v>
+        <v>-0.0003930221152007918</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.001025365092700633</v>
+        <v>0.002236351225924779</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.006412674916068411</v>
+        <v>-0.003390726552477324</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.002353232558808596</v>
+        <v>-0.004110418756603601</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.003852143485069084</v>
+        <v>-0.008083790592370329</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0002242597927053891</v>
+        <v>-0.0004684867140763133</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.487209994051053e-05</v>
+        <v>-0.0007221506587806792</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.00189293166302949</v>
+        <v>-0.001088786822265461</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.005884753558532277</v>
+        <v>-0.005344161732568536</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.0003479492207753343</v>
+        <v>-0.0002203672763820552</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.0007331684201114852</v>
+        <v>-0.0006461732257992487</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.0003012376245431214</v>
+        <v>0.000347271222288903</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.00246358032197404</v>
+        <v>-0.005110460714272147</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.0003051347913095998</v>
+        <v>-0.001061738326609774</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.0006377040224936209</v>
+        <v>-5.171397512622466e-05</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.004807750930726912</v>
+        <v>-0.003595574324195517</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.001506449346738284</v>
+        <v>-0.0008548913727084106</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.007530862154026416</v>
+        <v>-0.002846198124006469</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.003967938501436005</v>
+        <v>-0.0006024322815500304</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.002303048389022982</v>
+        <v>-0.003232920755157514</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.001015122937771803</v>
+        <v>-0.002868252444034216</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.178389982640475e-05</v>
+        <v>-0.000361448975355097</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.002078797512051889</v>
+        <v>0.0006451555024749006</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.0001449354270867203</v>
+        <v>0.0003946718182200771</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.009843414419748217</v>
+        <v>-0.00331862471996642</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.007204229772499257</v>
+        <v>-0.007106026832178186</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.0008420949568500008</v>
+        <v>-0.0004836843421941351</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.0002620830591700484</v>
+        <v>-0.000289001646815748</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.000564893250197454</v>
+        <v>-0.0008426966292135213</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.01039025457508485</v>
+        <v>-0.005535688900277946</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.002928562592045814</v>
+        <v>0.0007521741912817875</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.0004563085415739021</v>
+        <v>-0.0004069748996856609</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.001325794493750734</v>
+        <v>-0.001978662023135555</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.00497129700292997</v>
+        <v>-0.0005935134863450959</v>
       </c>
       <c r="BL6" t="n">
-        <v>-3.199987412702554e-05</v>
+        <v>-0.0008506323006011924</v>
       </c>
       <c r="BM6" t="n">
-        <v>5.648719781516098e-05</v>
+        <v>0.0008230483748657063</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.008381985130684211</v>
+        <v>-0.002945385139859407</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.0004272626842570542</v>
+        <v>-0.001287019973031939</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.001222092818686602</v>
+        <v>-0.002123133169655447</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-8.871179248466365e-05</v>
+        <v>-9.948735357729333e-05</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.001663279860368849</v>
+        <v>-0.002381465945329062</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.001283885639205751</v>
+        <v>-0.0004836814162221869</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.0009273564311574307</v>
+        <v>-0.0007280969046490254</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.001156320074702943</v>
+        <v>-0.001853874535007313</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.002580129454513017</v>
+        <v>-0.002300071436868706</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.001103257619277384</v>
+        <v>-0.001109795797573243</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.0002198680547899928</v>
+        <v>-8.043908836852263e-07</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.001304488326351871</v>
+        <v>-0.0008981782200214393</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.001708532826738387</v>
+        <v>-0.0009799280563809159</v>
       </c>
       <c r="CA6" t="n">
         <v>0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.00052542161727141</v>
+        <v>-0.000917068162107204</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.00186500876568263</v>
+        <v>-0.002883858872234119</v>
       </c>
       <c r="CD6" t="n">
-        <v>-2.2202486678502e-05</v>
+        <v>0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.0006710781131391341</v>
+        <v>-0.0003106247948161833</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.00252208335172972</v>
+        <v>-0.001188320501800871</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.0009413523170549388</v>
+        <v>-0.002487294629883613</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.002644104651506063</v>
+        <v>-0.0006290485534675816</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.000814055957134524</v>
+        <v>-0.001183479245953828</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0.001877143327590181</v>
+        <v>-0.001168283935511416</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.001736909468486847</v>
+        <v>-0.001323732227891089</v>
       </c>
     </row>
     <row r="7">
@@ -2232,268 +2232,268 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00064941793792056</v>
+        <v>-0.001371811836548398</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.001843613740384859</v>
+        <v>-0.003304810236968758</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001901073852957086</v>
+        <v>-0.0002540529199495766</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001509523786995615</v>
+        <v>0.001491472223988466</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0001180078189152167</v>
+        <v>0.0001188621147009405</v>
       </c>
       <c r="H7" t="n">
-        <v>0.003399138436342341</v>
+        <v>0.002570591027384628</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001070812503861707</v>
+        <v>-2.95945546019416e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.003441858804628039</v>
+        <v>-0.0009448256485191819</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01649879253865121</v>
+        <v>0.01772577993584287</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01742032728129563</v>
+        <v>0.02093079118453132</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0006292979145184008</v>
+        <v>-0.003926571247406913</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00113953490817017</v>
+        <v>0.0003554511133206483</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002279012870039288</v>
+        <v>0.00107965998364159</v>
       </c>
       <c r="P7" t="n">
-        <v>0.00607434531903378</v>
+        <v>0.003235413782191487</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.008321492527311042</v>
+        <v>0.01032754035487373</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.0009645228945355576</v>
+        <v>0.0005919305164013178</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0002101129835444582</v>
+        <v>0.0009114659333864848</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0003482298774418135</v>
+        <v>-0.001032458096126698</v>
       </c>
       <c r="U7" t="n">
-        <v>2.299123299548953e-05</v>
+        <v>-0.0004892406495928481</v>
       </c>
       <c r="V7" t="n">
-        <v>0.000248455484749821</v>
+        <v>0.0001500869761345003</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0008604951608046588</v>
+        <v>0.001101346346832482</v>
       </c>
       <c r="X7" t="n">
-        <v>-5.872479560842291e-06</v>
+        <v>0.0005552144717896113</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.003309434071250161</v>
+        <v>0.001495466357223807</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.00203339204686942</v>
+        <v>0.001557010428405203</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.002621852365081334</v>
+        <v>0.001058151974352367</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0001503706992106557</v>
+        <v>-0.0003302869525906027</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.003081810141725622</v>
+        <v>0.005598872171237446</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.002010567485420178</v>
+        <v>0.002421011907126553</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.0001400360428035208</v>
+        <v>-0.0004858077343179002</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.0006080382272280916</v>
+        <v>-0.00490872625071671</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0003982443180940876</v>
+        <v>-0.0003024480529783435</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0003048860054867486</v>
+        <v>4.455801856306785e-05</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.001035475500701471</v>
+        <v>-0.0007376115506029124</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.002454243593114802</v>
+        <v>-0.002822608561689299</v>
       </c>
       <c r="AL7" t="n">
-        <v>-1.380337400829213e-05</v>
+        <v>6.094145408592211e-05</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.0003404526713656042</v>
+        <v>-0.0002237680842984202</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.001811848622971241</v>
+        <v>0.001785224977984307</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.000487444608567178</v>
+        <v>0.00148326899740518</v>
       </c>
       <c r="AP7" t="n">
-        <v>-7.468481900281821e-05</v>
+        <v>0.0004244302355698726</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.001239801072175134</v>
+        <v>0.001358731709434085</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.0024440970658337</v>
+        <v>-0.001018261476747673</v>
       </c>
       <c r="AS7" t="n">
-        <v>-9.711119762145223e-05</v>
+        <v>0.002438436657270648</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.0007542870291521008</v>
+        <v>0.005574519551454571</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.002441914334890843</v>
+        <v>0.0007163129344401221</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.0001707511532545835</v>
+        <v>-0.002256453241345596</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.001021270582364425</v>
+        <v>-0.001004508880567889</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0003689625897381366</v>
+        <v>-0.000117924600173891</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.0009226270649070834</v>
+        <v>0.001524212305825734</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.001585958980244095</v>
+        <v>0.0033756171017995</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.0003137119083498951</v>
+        <v>-0.001225677653795848</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.0009074442439800324</v>
+        <v>-0.001463583604468916</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0003932418694138851</v>
+        <v>4.099484511136395e-05</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.0001663407035168762</v>
+        <v>0.0004571363146211538</v>
       </c>
       <c r="BE7" t="n">
-        <v>-8.849561376954586e-05</v>
+        <v>-0.0004504181618774195</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.001048365692819658</v>
+        <v>-0.003751185715632105</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.002398286589816667</v>
+        <v>0.002517419840816359</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.0002812314979277752</v>
+        <v>2.61537586894178e-06</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.002868460706299314</v>
+        <v>-0.0009209843793313077</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.000546322937127891</v>
+        <v>0.001402074399076386</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0002944214050591198</v>
+        <v>-0.0003086941793772391</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.002109586894554089</v>
+        <v>0.002388556932976555</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0.003691015754368504</v>
+        <v>-0.0006039403111982478</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0006060064268706422</v>
+        <v>0.001126238294214704</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.001648259123652623</v>
+        <v>-0.0006891967256878184</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.610918725903024e-05</v>
+        <v>7.380321950026803e-05</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0.0005552234978854654</v>
+        <v>-0.0001212214787101428</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.0003778777810017563</v>
+        <v>0.0001179847900600772</v>
       </c>
       <c r="BT7" t="n">
-        <v>-5.195898868805006e-05</v>
+        <v>3.21756353470205e-06</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.003958284901454778</v>
+        <v>0.004090518361258271</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.0003567519587264313</v>
+        <v>0.0009270277688493145</v>
       </c>
       <c r="BW7" t="n">
-        <v>-0.0001175415019453285</v>
+        <v>0.001786922631434551</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0.0001181950514032137</v>
+        <v>0.0001362398074149229</v>
       </c>
       <c r="BY7" t="n">
-        <v>6.406164666084013e-05</v>
+        <v>-0.0002859872316501255</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.0009867726824901945</v>
+        <v>-0.0003400647757024644</v>
       </c>
       <c r="CA7" t="n">
         <v>0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0.0003180411299014141</v>
+        <v>-7.372456502505176e-05</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.002464253370725688</v>
+        <v>0.0007351730588903815</v>
       </c>
       <c r="CD7" t="n">
         <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.0002913952151334442</v>
+        <v>-0.0002367306942785419</v>
       </c>
       <c r="CF7" t="n">
-        <v>-0.001259295391394549</v>
+        <v>0.0006169378011901872</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.001055998230149263</v>
+        <v>-0.0003573045117699514</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.0007246207022870766</v>
+        <v>-0.0001222493887530818</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.0006644731981752694</v>
+        <v>-0.0004570729357977921</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.0001318940091222299</v>
+        <v>0.00121208313611062</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0004049398142965066</v>
+        <v>-0.0004429223764182256</v>
       </c>
     </row>
     <row r="8">
@@ -2503,268 +2503,268 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002163368866805582</v>
+        <v>0.003087462190419113</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003382317315164515</v>
+        <v>0.001688031181679547</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003291204921494748</v>
+        <v>0.00448247157468423</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00358404779171923</v>
+        <v>0.002667982955482892</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001963735701017258</v>
+        <v>0.001915172241723073</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004325067961988407</v>
+        <v>0.003645791522666847</v>
       </c>
       <c r="I8" t="n">
-        <v>0.000146534338707896</v>
+        <v>5.198441063792303e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002936983451426736</v>
+        <v>0.0005161726281483564</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02018417747712353</v>
+        <v>0.02395310246666461</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02217046426220765</v>
+        <v>0.0250599829015317</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0006502147057922875</v>
+        <v>-0.002023902044101358</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003721337667687644</v>
+        <v>0.001088234710211122</v>
       </c>
       <c r="O8" t="n">
-        <v>0.005634715742985563</v>
+        <v>0.002162572342489108</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01598367497884291</v>
+        <v>0.01688898437615231</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01512968972304127</v>
+        <v>0.01819631964594796</v>
       </c>
       <c r="R8" t="n">
-        <v>0.002102499845274084</v>
+        <v>0.002713416401824567</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0006830037841286968</v>
+        <v>0.002780694733262137</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001406729238150336</v>
+        <v>0.001236188256835657</v>
       </c>
       <c r="U8" t="n">
-        <v>0.003184299785784511</v>
+        <v>0.00201312182181522</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0004724471835967692</v>
+        <v>0.0005360984259959762</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003694419614000677</v>
+        <v>0.004053676026887184</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0008426205546349097</v>
+        <v>0.002392159523587856</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.004037145213046015</v>
+        <v>0.003629374164928056</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.003410568381459797</v>
+        <v>0.003157486932549999</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003433383912235427</v>
+        <v>0.001714847584041648</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0004644657319392564</v>
+        <v>-0.000239928861962671</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.005911281614197609</v>
+        <v>0.006250934865726554</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.002121892647564244</v>
+        <v>0.004593977992902234</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.003799060468135024</v>
+        <v>0.002818822122667503</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.005147423726311446</v>
+        <v>0.001696346428103823</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0007231550764981775</v>
+        <v>0.0003033485651547124</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0004932916710653573</v>
+        <v>0.0008622003871079809</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.001314684556339463</v>
+        <v>0.001167373491051946</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.001505437547168595</v>
+        <v>0.0006351364967427525</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0005406999105619703</v>
+        <v>0.0004006797841952153</v>
       </c>
       <c r="AM8" t="n">
-        <v>-8.862657091800175e-05</v>
+        <v>-1.261174042471447e-05</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.00353400221680954</v>
+        <v>0.002799219833961858</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.001793305525877198</v>
+        <v>0.003408352751032473</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0008253675273429489</v>
+        <v>0.001768280905499664</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.002238823049254476</v>
+        <v>0.003452750168773261</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.0006592085570208434</v>
+        <v>0.0005118137548181551</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.002263783013388154</v>
+        <v>0.004691074201731152</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.001228915639178374</v>
+        <v>0.007560698588164805</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.0006244397486386859</v>
+        <v>0.002311836552535076</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.002072756003520729</v>
+        <v>0.0014496064679696</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.002643494895157214</v>
+        <v>0.0008158909821613519</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.00047525047069297</v>
+        <v>0.0005219820039745083</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.003003601817203114</v>
+        <v>0.002359973796985507</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.002642001402304356</v>
+        <v>0.005270446668697199</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.00211367468720268</v>
+        <v>0.001088247415825807</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.003987133708162937</v>
+        <v>0.001575596023623174</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.000676056646941789</v>
+        <v>0.001405400975669008</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0004734081768118348</v>
+        <v>0.001024786923680901</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.340093603742099e-05</v>
+        <v>-8.866563530153804e-05</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.003749353679824266</v>
+        <v>-1.555465875743844e-05</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.001535587711252689</v>
+        <v>0.005233132063668822</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0009132699551948009</v>
+        <v>0.0002110637810034344</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.004088031537269144</v>
+        <v>0.003145449310386722</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.002100381748677951</v>
+        <v>0.002959621918613744</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.001157985620743848</v>
+        <v>0.0008600111538853928</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.002661637642536899</v>
+        <v>0.004328345651327678</v>
       </c>
       <c r="BN8" t="n">
-        <v>-0.001327690925410133</v>
+        <v>0.001368605025349262</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.0008216283707528083</v>
+        <v>0.003690937282499271</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.00381278559857314</v>
+        <v>0.0009622555417314161</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.000217769835487791</v>
+        <v>0.0001119730819160253</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.004220048612131089</v>
+        <v>0.003889694248931855</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.002791807887748238</v>
+        <v>0.002937780372407462</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0004731788158030158</v>
+        <v>0.0006206316972541371</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.007603298351928154</v>
+        <v>0.01485717439354767</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.002511003439914772</v>
+        <v>0.002419291565185386</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.001714974105180933</v>
+        <v>0.003661638240806286</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0001331690065092511</v>
+        <v>0.0003539637818745861</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0005125591317863998</v>
+        <v>0.0004846217482377207</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.0002238612929904349</v>
+        <v>4.68018720748753e-05</v>
       </c>
       <c r="CA8" t="n">
         <v>0</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0002801402792255048</v>
+        <v>0.0006480355128947512</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.003770247892792338</v>
+        <v>0.001295096351109717</v>
       </c>
       <c r="CD8" t="n">
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0001616194461212528</v>
+        <v>0.0001110124333925266</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.003310871184320838</v>
+        <v>0.0022912439253787</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.00254057631741986</v>
+        <v>0.004142418630730524</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.0002389346185094537</v>
+        <v>0.0001264519348407434</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.001416420701771898</v>
+        <v>0.002190247952796021</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.003844622745278726</v>
+        <v>0.007630970425317876</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.001755820428326796</v>
+        <v>0.001942957596944583</v>
       </c>
     </row>
     <row r="9">
@@ -2774,268 +2774,268 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.005073349633251856</v>
+        <v>0.0146564435269832</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.006307102858826963</v>
+        <v>0.01326259946949602</v>
       </c>
       <c r="E9" t="n">
-        <v>0.009307427138827918</v>
+        <v>0.01068630523346916</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005413444378346266</v>
+        <v>0.005762028233938288</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002772043644942435</v>
+        <v>0.00757441791924549</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01273960483633141</v>
+        <v>0.005978584176085666</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0002654084340902085</v>
+        <v>0.0006216696269982335</v>
       </c>
       <c r="J9" t="n">
-        <v>0.007397583259652185</v>
+        <v>0.005023400936037414</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04158561744768639</v>
+        <v>0.03978779840848806</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05520188623636897</v>
+        <v>0.0399351606248158</v>
       </c>
       <c r="M9" t="n">
-        <v>0.007013909440662924</v>
+        <v>0.006510802012429706</v>
       </c>
       <c r="N9" t="n">
-        <v>0.009873268493958132</v>
+        <v>0.007207771858351641</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0242558208075449</v>
+        <v>0.02257589154140877</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0193748156885874</v>
+        <v>0.02489859594383773</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03135867963454168</v>
+        <v>0.02788093132920717</v>
       </c>
       <c r="R9" t="n">
-        <v>0.004436761740132545</v>
+        <v>0.006218685529030332</v>
       </c>
       <c r="S9" t="n">
-        <v>0.00336184016514296</v>
+        <v>0.003627248599233268</v>
       </c>
       <c r="T9" t="n">
-        <v>0.003625110521662222</v>
+        <v>0.004512691946098402</v>
       </c>
       <c r="U9" t="n">
-        <v>0.006754278728606377</v>
+        <v>0.003094606542882394</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0007138607971446054</v>
+        <v>0.0008112324492979605</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0256112469437653</v>
+        <v>0.01656479217603907</v>
       </c>
       <c r="X9" t="n">
-        <v>0.002130993418990901</v>
+        <v>0.004011281729865257</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.005348410757946231</v>
+        <v>0.004479811376363075</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.007102858826996727</v>
+        <v>0.00377535101404054</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.006799193316047269</v>
+        <v>0.00633510953226758</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001006512729425701</v>
+        <v>0.001843849034860223</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.01157489638839553</v>
+        <v>0.01175251628182357</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.008873523480265077</v>
+        <v>0.009737827715355774</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.005179047055341834</v>
+        <v>0.007102693104468772</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.007132287659070735</v>
+        <v>0.00495142588530244</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001094785364448314</v>
+        <v>0.001178897730621864</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.001065403965670297</v>
+        <v>0.002711464780430261</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.008256880733944972</v>
+        <v>0.003255401006214853</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.005416306539902049</v>
+        <v>0.005214635551714142</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.00180526783071917</v>
+        <v>0.001002063071028569</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.001184132622853784</v>
+        <v>0.0009470257472624866</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.005145746579417054</v>
+        <v>0.008111308466548228</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.002381698527107468</v>
+        <v>0.007646505797555636</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.001279000594884017</v>
+        <v>0.004980842911877392</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.007721780135573198</v>
+        <v>0.005897965202005318</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.001296456352636133</v>
+        <v>0.003053874963987269</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.005358200118413292</v>
+        <v>0.006631299734747975</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.005553914327917364</v>
+        <v>0.01304212168486736</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.002974419988102339</v>
+        <v>0.007634687409968255</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.006998777506112486</v>
+        <v>0.005956944854025381</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.01020782396088021</v>
+        <v>0.007223208999407915</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.001516954193932196</v>
+        <v>0.001728608470181448</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.006303640130216048</v>
+        <v>0.008429118773946342</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.01014040561622462</v>
+        <v>0.010242747187685</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.008753315649867343</v>
+        <v>0.009608016504568228</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.008079313406333267</v>
+        <v>0.006836342113051208</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.001154529307282448</v>
+        <v>0.001915708812260519</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.000884173297966373</v>
+        <v>0.002485942586564083</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.0001222493887530596</v>
+        <v>0.000218408736349418</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.009413202933985333</v>
+        <v>0.01009174311926607</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.01317668054729332</v>
+        <v>0.01409117821195975</v>
       </c>
       <c r="BH9" t="n">
+        <v>1.110223024625157e-17</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0.0007992895204262717</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.004669839381320651</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.005249189029784751</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.002418165732822175</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.007401946328516673</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0.005982905982905984</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.00616337363609557</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.002381698527107512</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0.004465571881302155</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.01155286660904632</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0.008959953903774076</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0.00348602708153265</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0.02167502211736953</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.005390159824506436</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0.0104099085815394</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0.001181215787957302</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0.00590607893978673</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.0009766203018644394</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>5.762028233937677e-05</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0.006972054163065356</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0.002601065496709509</v>
+      </c>
+      <c r="CD9" t="n">
         <v>0</v>
       </c>
-      <c r="BI9" t="n">
-        <v>0.00165366614664586</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0.005745721271393655</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>0.005073349633251867</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0.001503981126511322</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>0.004699583581201716</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>0.003552397868561319</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>0.003777513384889975</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>0.01400172860847021</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>0.001008354940939216</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>0.01022760011524058</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>0.003463338533541349</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>0.001584557764333083</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>0.01371362719677328</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>0.00769230769230772</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>0.0132704217045119</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>0.0004718372161603868</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>0.002852203975799483</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>0.000296033155713471</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>0.0002072232089994297</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>0.003255545952175187</v>
-      </c>
-      <c r="CC9" t="n">
-        <v>0.008762581409117842</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>0.0002507051081165557</v>
-      </c>
       <c r="CE9" t="n">
-        <v>0.001503981126511311</v>
+        <v>0.003975799481417397</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.004324663115010963</v>
+        <v>0.008053901598245049</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.007193605683836623</v>
+        <v>0.008671852492077159</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.001361752516281844</v>
+        <v>0.004148660328435539</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.002215657311669195</v>
+        <v>0.004436761740132478</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.006864274570982809</v>
+        <v>0.01351195620858536</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.003837753510140385</v>
+        <v>0.00279458369346004</v>
       </c>
     </row>
   </sheetData>
